--- a/MR_UKBiobank/BinaryData/Logistic/gMR_dat.xlsx
+++ b/MR_UKBiobank/BinaryData/Logistic/gMR_dat.xlsx
@@ -64,10 +64,16 @@
     <t>p.outcome</t>
   </si>
   <si>
+    <t>outcome</t>
+  </si>
+  <si>
     <t>n.outcome</t>
   </si>
   <si>
-    <t>outcome</t>
+    <t>case.outcome</t>
+  </si>
+  <si>
+    <t>controls.outcome</t>
   </si>
   <si>
     <t>pval.exposure</t>
@@ -83,12 +89,6 @@
   </si>
   <si>
     <t>exposure</t>
-  </si>
-  <si>
-    <t>beta.exposure_corrected</t>
-  </si>
-  <si>
-    <t>se.exposure_corrected</t>
   </si>
   <si>
     <t>action</t>
@@ -327,13 +327,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05852301000398645</v>
+        <v>0.058638626550495024</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38617586648368346</v>
+        <v>0.5424335230809182</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -348,37 +348,37 @@
         <v>44</v>
       </c>
       <c r="O2" t="n">
-        <v>0.014706108026039059</v>
+        <v>0.017081615851643233</v>
       </c>
       <c r="P2" t="n">
-        <v>6.90593110046539E-5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>5.97272231591968E-4</v>
+      </c>
+      <c r="Q2" t="s">
         <v>44</v>
       </c>
+      <c r="R2" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S2" t="n">
+        <v>22073.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>220530.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -413,13 +413,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06057742191195994</v>
+        <v>-0.057853611776184574</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2855965220915346</v>
+        <v>0.34723808032052367</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -434,37 +434,37 @@
         <v>44</v>
       </c>
       <c r="O3" t="n">
-        <v>0.012263825341104383</v>
+        <v>0.01425034685900134</v>
       </c>
       <c r="P3" t="n">
-        <v>7.831473916187852E-7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>4.911397598353995E-5</v>
+      </c>
+      <c r="Q3" t="s">
         <v>44</v>
       </c>
+      <c r="R3" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S3" t="n">
+        <v>22073.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>220530.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -499,13 +499,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08657116914557775</v>
+        <v>0.06583036304117222</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018309748848942</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -520,37 +520,37 @@
         <v>44</v>
       </c>
       <c r="O4" t="n">
-        <v>0.016678973778723176</v>
+        <v>0.019283719131473427</v>
       </c>
       <c r="P4" t="n">
-        <v>2.098006599721131E-7</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>6.406842958793689E-4</v>
+      </c>
+      <c r="Q4" t="s">
         <v>44</v>
       </c>
+      <c r="R4" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S4" t="n">
+        <v>22073.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>220530.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -585,13 +585,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.09435562977425106</v>
+        <v>-0.07478435937862167</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07152001915797036</v>
+        <v>0.0739026310474314</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -606,37 +606,37 @@
         <v>44</v>
       </c>
       <c r="O5" t="n">
-        <v>0.017888019338047623</v>
+        <v>0.020704876623677898</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3290477895093088E-7</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>3.03938258460264E-4</v>
+      </c>
+      <c r="Q5" t="s">
         <v>44</v>
       </c>
+      <c r="R5" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S5" t="n">
+        <v>22073.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>220530.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -671,13 +671,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.055310828736900575</v>
+        <v>-0.04887132268903477</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.255307586740474</v>
+        <v>0.3023767224642729</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -692,37 +692,37 @@
         <v>44</v>
       </c>
       <c r="O6" t="n">
-        <v>0.012175680748497439</v>
+        <v>0.014148707217865854</v>
       </c>
       <c r="P6" t="n">
-        <v>5.5530388485653914E-6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>5.520930866333066E-4</v>
+      </c>
+      <c r="Q6" t="s">
         <v>44</v>
       </c>
+      <c r="R6" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S6" t="n">
+        <v>22073.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>220530.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -757,13 +757,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.09961683158859869</v>
+        <v>-0.08337262422992475</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07840491475624246</v>
+        <v>0.08128300144680815</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -778,37 +778,37 @@
         <v>44</v>
       </c>
       <c r="O7" t="n">
-        <v>0.017231222866866014</v>
+        <v>0.01996182465966161</v>
       </c>
       <c r="P7" t="n">
-        <v>7.417768735741478E-9</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>2.9589430332170737E-5</v>
+      </c>
+      <c r="Q7" t="s">
         <v>44</v>
       </c>
+      <c r="R7" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S7" t="n">
+        <v>22073.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>220530.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -937,13 +937,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.022876151624338956</v>
+        <v>-0.027690063523554548</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38617586648368346</v>
+        <v>0.5424335230809182</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -958,37 +958,37 @@
         <v>47</v>
       </c>
       <c r="O2" t="n">
-        <v>0.015523722780576893</v>
+        <v>0.018089252517253764</v>
       </c>
       <c r="P2" t="n">
-        <v>0.14058248846438318</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.1258320081267839</v>
+      </c>
+      <c r="Q2" t="s">
         <v>47</v>
       </c>
+      <c r="R2" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S2" t="n">
+        <v>19190.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>223413.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -1023,13 +1023,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.024538082625255815</v>
+        <v>0.014255055983260179</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2855965220915346</v>
+        <v>0.34723808032052367</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -1044,37 +1044,37 @@
         <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>0.013236359345181076</v>
+        <v>0.015415817649638735</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06376215971987187</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.3551203120068869</v>
+      </c>
+      <c r="Q3" t="s">
         <v>47</v>
       </c>
+      <c r="R3" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S3" t="n">
+        <v>19190.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>223413.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -1109,13 +1109,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.018248869437388706</v>
+        <v>-0.021858841374728953</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018309748848942</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -1130,37 +1130,37 @@
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>0.017419398346154382</v>
+        <v>0.02030462921415059</v>
       </c>
       <c r="P4" t="n">
-        <v>0.29481479490083357</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.2816837118964371</v>
+      </c>
+      <c r="Q4" t="s">
         <v>47</v>
       </c>
+      <c r="R4" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S4" t="n">
+        <v>19190.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>223413.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -1195,13 +1195,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03355083544427332</v>
+        <v>0.03696006155216058</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07152001915797036</v>
+        <v>0.0739026310474314</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -1216,37 +1216,37 @@
         <v>47</v>
       </c>
       <c r="O5" t="n">
-        <v>0.018499962349236128</v>
+        <v>0.021612906241940646</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06974512920472323</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.08724883204108519</v>
+      </c>
+      <c r="Q5" t="s">
         <v>47</v>
       </c>
+      <c r="R5" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S5" t="n">
+        <v>19190.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>223413.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -1281,13 +1281,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.031249891139248732</v>
+        <v>0.03597271144416821</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.255307586740474</v>
+        <v>0.3023767224642729</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -1302,37 +1302,37 @@
         <v>47</v>
       </c>
       <c r="O6" t="n">
-        <v>0.013088108419160105</v>
+        <v>0.015255482918716227</v>
       </c>
       <c r="P6" t="n">
-        <v>0.016956238109518375</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.018372775703735186</v>
+      </c>
+      <c r="Q6" t="s">
         <v>47</v>
       </c>
+      <c r="R6" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S6" t="n">
+        <v>19190.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>223413.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -1367,13 +1367,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.028143938473642677</v>
+        <v>0.027199716130210782</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07840491475624246</v>
+        <v>0.08128300144680815</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -1388,37 +1388,37 @@
         <v>47</v>
       </c>
       <c r="O7" t="n">
-        <v>0.017841604329860948</v>
+        <v>0.020866632577861616</v>
       </c>
       <c r="P7" t="n">
-        <v>0.11469588818011912</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.1924031261145366</v>
+      </c>
+      <c r="Q7" t="s">
         <v>47</v>
       </c>
+      <c r="R7" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S7" t="n">
+        <v>19190.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>223413.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -1547,13 +1547,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.018461384409979027</v>
+        <v>-0.03351992111825264</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38617586648368346</v>
+        <v>0.5424335230809182</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -1568,37 +1568,37 @@
         <v>48</v>
       </c>
       <c r="O2" t="n">
-        <v>0.019048266001714085</v>
+        <v>0.022354566677166413</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3324505178076055</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.13375268484687677</v>
+      </c>
+      <c r="Q2" t="s">
         <v>48</v>
       </c>
+      <c r="R2" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S2" t="n">
+        <v>12047.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>230556.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -1633,13 +1633,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03261748736920863</v>
+        <v>0.01994359683525964</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2855965220915346</v>
+        <v>0.34723808032052367</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -1654,37 +1654,37 @@
         <v>48</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01624168933907146</v>
+        <v>0.01909059463106244</v>
       </c>
       <c r="P3" t="n">
-        <v>0.044615981774844375</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.2961700574406997</v>
+      </c>
+      <c r="Q3" t="s">
         <v>48</v>
       </c>
+      <c r="R3" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S3" t="n">
+        <v>12047.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>230556.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -1719,13 +1719,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.027049316458251003</v>
+        <v>-0.03880878470998141</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018309748848942</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -1740,37 +1740,37 @@
         <v>48</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02129732964239767</v>
+        <v>0.02500193294663108</v>
       </c>
       <c r="P4" t="n">
-        <v>0.20405606765255724</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.12060687181714269</v>
+      </c>
+      <c r="Q4" t="s">
         <v>48</v>
       </c>
+      <c r="R4" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S4" t="n">
+        <v>12047.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>230556.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -1805,13 +1805,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0019502379566337326</v>
+        <v>-0.0059922764426209845</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07152001915797036</v>
+        <v>0.0739026310474314</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -1826,37 +1826,37 @@
         <v>48</v>
       </c>
       <c r="O5" t="n">
-        <v>0.022910329051921627</v>
+        <v>0.027087129843778826</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9321621473110449</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.8249193672390334</v>
+      </c>
+      <c r="Q5" t="s">
         <v>48</v>
       </c>
+      <c r="R5" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S5" t="n">
+        <v>12047.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>230556.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -1891,13 +1891,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02159258312629346</v>
+        <v>0.028972149096587803</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.255307586740474</v>
+        <v>0.3023767224642729</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -1912,37 +1912,37 @@
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01604694773513733</v>
+        <v>0.018882176929497955</v>
       </c>
       <c r="P6" t="n">
-        <v>0.17843536714676128</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.12493991308558938</v>
+      </c>
+      <c r="Q6" t="s">
         <v>48</v>
       </c>
+      <c r="R6" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S6" t="n">
+        <v>12047.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>230556.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -1977,13 +1977,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00876437411683533</v>
+        <v>-0.005594306923182715</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07840491475624246</v>
+        <v>0.08128300144680815</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -1998,37 +1998,37 @@
         <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>0.021987228070259737</v>
+        <v>0.026071555748659818</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6901790792852229</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.8300986018467406</v>
+      </c>
+      <c r="Q7" t="s">
         <v>48</v>
       </c>
+      <c r="R7" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S7" t="n">
+        <v>12047.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>230556.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -2157,13 +2157,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007015026789195248</v>
+        <v>6.831759950181617E-4</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38617586648368346</v>
+        <v>0.5424335230809182</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -2178,37 +2178,37 @@
         <v>49</v>
       </c>
       <c r="O2" t="n">
-        <v>0.029314722086765454</v>
+        <v>0.034322756530732274</v>
       </c>
       <c r="P2" t="n">
-        <v>0.810872600565911</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.9841195858777936</v>
+      </c>
+      <c r="Q2" t="s">
         <v>49</v>
       </c>
+      <c r="R2" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S2" t="n">
+        <v>4950.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>237653.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -2243,13 +2243,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.012385428496962397</v>
+        <v>-0.007771591558606496</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2855965220915346</v>
+        <v>0.34723808032052367</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -2264,37 +2264,37 @@
         <v>49</v>
       </c>
       <c r="O3" t="n">
-        <v>0.024770176724765183</v>
+        <v>0.029036547372713283</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6170654086327142</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.788969809767228</v>
+      </c>
+      <c r="Q3" t="s">
         <v>49</v>
       </c>
+      <c r="R3" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S3" t="n">
+        <v>4950.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>237653.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -2329,13 +2329,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0030275900167045025</v>
+        <v>0.018653373136791922</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018309748848942</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -2350,37 +2350,37 @@
         <v>49</v>
       </c>
       <c r="O4" t="n">
-        <v>0.032857782726198936</v>
+        <v>0.038745920128109276</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9265850208984425</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.6302122981891447</v>
+      </c>
+      <c r="Q4" t="s">
         <v>49</v>
       </c>
+      <c r="R4" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S4" t="n">
+        <v>4950.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>237653.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -2415,13 +2415,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007581424790600065</v>
+        <v>0.035649255492292406</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07152001915797036</v>
+        <v>0.0739026310474314</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -2436,37 +2436,37 @@
         <v>49</v>
       </c>
       <c r="O5" t="n">
-        <v>0.034939301597954366</v>
+        <v>0.04067957746609613</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8282173484673135</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.38084369509112515</v>
+      </c>
+      <c r="Q5" t="s">
         <v>49</v>
       </c>
+      <c r="R5" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S5" t="n">
+        <v>4950.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>237653.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -2501,13 +2501,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.016101449522963038</v>
+        <v>0.012443810234865004</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.255307586740474</v>
+        <v>0.3023767224642729</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -2522,37 +2522,37 @@
         <v>49</v>
       </c>
       <c r="O6" t="n">
-        <v>0.024536669273799668</v>
+        <v>0.02876672852079299</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5116826763564092</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.6653224776727242</v>
+      </c>
+      <c r="Q6" t="s">
         <v>49</v>
       </c>
+      <c r="R6" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S6" t="n">
+        <v>4950.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>237653.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -2587,13 +2587,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.012755970865085</v>
+        <v>0.010690190832036131</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07840491475624246</v>
+        <v>0.08128300144680815</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -2608,37 +2608,37 @@
         <v>49</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03387531050553985</v>
+        <v>0.03950965418171173</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7065031650257299</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.7867205317697467</v>
+      </c>
+      <c r="Q7" t="s">
         <v>49</v>
       </c>
+      <c r="R7" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S7" t="n">
+        <v>4950.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>237653.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -2767,13 +2767,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0075423328999804536</v>
+        <v>2.8761634375579985E-4</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38617586648368346</v>
+        <v>0.5424335230809182</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -2788,37 +2788,37 @@
         <v>50</v>
       </c>
       <c r="O2" t="n">
-        <v>0.008572143944722537</v>
+        <v>0.009952867086715285</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3789322279754317</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.9769460696849486</v>
+      </c>
+      <c r="Q2" t="s">
         <v>50</v>
       </c>
+      <c r="R2" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S2" t="n">
+        <v>97298.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>145305.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -2853,13 +2853,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.641269727342004E-4</v>
+        <v>0.0023241198681578272</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2855965220915346</v>
+        <v>0.34723808032052367</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -2874,37 +2874,37 @@
         <v>50</v>
       </c>
       <c r="O3" t="n">
-        <v>0.007259920288599034</v>
+        <v>0.008431672005252825</v>
       </c>
       <c r="P3" t="n">
-        <v>0.927112350301289</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.7828233268952862</v>
+      </c>
+      <c r="Q3" t="s">
         <v>50</v>
       </c>
+      <c r="R3" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S3" t="n">
+        <v>97298.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>145305.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -2939,13 +2939,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0026409784804478855</v>
+        <v>-0.009631237479610276</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018309748848942</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -2960,37 +2960,37 @@
         <v>50</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009614765491649134</v>
+        <v>0.011170588184359365</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7835625219492152</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.3885796197774779</v>
+      </c>
+      <c r="Q4" t="s">
         <v>50</v>
       </c>
+      <c r="R4" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S4" t="n">
+        <v>97298.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>145305.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -3025,13 +3025,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.017835853848220305</v>
+        <v>0.02004014367591</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07152001915797036</v>
+        <v>0.0739026310474314</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -3046,37 +3046,37 @@
         <v>50</v>
       </c>
       <c r="O5" t="n">
-        <v>0.010249286011494803</v>
+        <v>0.011928762959419296</v>
       </c>
       <c r="P5" t="n">
-        <v>0.08182311216962376</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.0929602206040071</v>
+      </c>
+      <c r="Q5" t="s">
         <v>50</v>
       </c>
+      <c r="R5" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S5" t="n">
+        <v>97298.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>145305.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -3111,13 +3111,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.005059415101179245</v>
+        <v>-0.004000147808344744</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.255307586740474</v>
+        <v>0.3023767224642729</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -3132,37 +3132,37 @@
         <v>50</v>
       </c>
       <c r="O6" t="n">
-        <v>0.007187042130393239</v>
+        <v>0.008347851913398235</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4814555245876734</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.6318085250209495</v>
+      </c>
+      <c r="Q6" t="s">
         <v>50</v>
       </c>
+      <c r="R6" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S6" t="n">
+        <v>97298.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>145305.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -3197,13 +3197,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.015763325962053525</v>
+        <v>0.01939462895288402</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07840491475624246</v>
+        <v>0.08128300144680815</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -3218,37 +3218,37 @@
         <v>50</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009870504839532435</v>
+        <v>0.011484904862572129</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1102627774549187</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.09127576518208075</v>
+      </c>
+      <c r="Q7" t="s">
         <v>50</v>
       </c>
+      <c r="R7" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S7" t="n">
+        <v>97298.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>145305.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -3377,13 +3377,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.03291768735651441</v>
+        <v>-0.025365637665085015</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38617586648368346</v>
+        <v>0.5424335230809182</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -3398,37 +3398,37 @@
         <v>51</v>
       </c>
       <c r="O2" t="n">
-        <v>0.014156466496240019</v>
+        <v>0.0165729690881876</v>
       </c>
       <c r="P2" t="n">
-        <v>0.020057223491899808</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R2" t="s">
+        <v>0.1258824404722021</v>
+      </c>
+      <c r="Q2" t="s">
         <v>51</v>
       </c>
+      <c r="R2" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S2" t="n">
+        <v>22827.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>219776.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -3463,13 +3463,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.013143179423704222</v>
+        <v>0.016840318673706264</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2855965220915346</v>
+        <v>0.34723808032052367</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -3484,37 +3484,37 @@
         <v>51</v>
       </c>
       <c r="O3" t="n">
-        <v>0.012085688651311455</v>
+        <v>0.014122637744719035</v>
       </c>
       <c r="P3" t="n">
-        <v>0.27681615384009317</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R3" t="s">
+        <v>0.2330909694421584</v>
+      </c>
+      <c r="Q3" t="s">
         <v>51</v>
       </c>
+      <c r="R3" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S3" t="n">
+        <v>22827.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>219776.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -3549,13 +3549,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04249482655464368</v>
+        <v>-0.0451874995156372</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018309748848942</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -3570,37 +3570,37 @@
         <v>51</v>
       </c>
       <c r="O4" t="n">
-        <v>0.015820910871693763</v>
+        <v>0.018487274017106304</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007231500464492473</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R4" t="s">
+        <v>0.014515407766472005</v>
+      </c>
+      <c r="Q4" t="s">
         <v>51</v>
       </c>
+      <c r="R4" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S4" t="n">
+        <v>22827.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>219776.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -3635,13 +3635,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02506469891272249</v>
+        <v>0.023372306838381752</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07152001915797036</v>
+        <v>0.0739026310474314</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -3656,37 +3656,37 @@
         <v>51</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0169437037706899</v>
+        <v>0.01985930746798764</v>
       </c>
       <c r="P5" t="n">
-        <v>0.13906207761814324</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0.23923767577927174</v>
+      </c>
+      <c r="Q5" t="s">
         <v>51</v>
       </c>
+      <c r="R5" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S5" t="n">
+        <v>22827.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>219776.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -3721,13 +3721,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01153086646002504</v>
+        <v>0.009497078247266639</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.255307586740474</v>
+        <v>0.3023767224642729</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -3742,37 +3742,37 @@
         <v>51</v>
       </c>
       <c r="O6" t="n">
-        <v>0.011956358439186417</v>
+        <v>0.013970100832988558</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3348389512362645</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R6" t="s">
+        <v>0.4966218728547569</v>
+      </c>
+      <c r="Q6" t="s">
         <v>51</v>
       </c>
+      <c r="R6" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S6" t="n">
+        <v>22827.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>219776.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -3807,13 +3807,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0161210675852458</v>
+        <v>0.020234021231938393</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07840491475624246</v>
+        <v>0.08128300144680815</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -3828,37 +3828,37 @@
         <v>51</v>
       </c>
       <c r="O7" t="n">
-        <v>0.016358578357047373</v>
+        <v>0.0191408151600237</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3243878769087194</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>325713.0</v>
-      </c>
-      <c r="R7" t="s">
+        <v>0.2904596208321307</v>
+      </c>
+      <c r="Q7" t="s">
         <v>51</v>
       </c>
+      <c r="R7" t="n">
+        <v>242603.0</v>
+      </c>
       <c r="S7" t="n">
+        <v>22827.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>219776.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
